--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260706.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260706.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>904,244,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.37%</t>
+          <t>10.53%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>899,244,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.34%</t>
+          <t>10.41%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>185,192,000</t>
+          <t>185,302,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.27%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,999,000</t>
+          <t>5,005,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>31,116,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>30,866,000</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
@@ -924,161 +924,161 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>148,092,000</t>
+          <t>132,597,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>131,997,000</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>149,092,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,615</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>1,516</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>99,767,000</t>
+          <t>371,675,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>371,675,000</t>
+          <t>100,367,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1117,78 +1117,78 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>80,788,000</t>
+          <t>81,388,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>277,366,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>178,956,000</t>
+          <t>279,366,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>178,956,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,523,000</t>
+          <t>14,603,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,736,080,464</t>
+          <t>7,043,565,312</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>7,131,336,703</t>
+          <t>7,092,270,248</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-132,885,655</t>
+          <t>-66,264,382</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
